--- a/data/trans_camb/IP16B06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Habitat-trans_camb.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-78,5; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 0,0</t>
+          <t>-55,33; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP16B06-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B06-Habitat-trans_camb.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-78,5; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 0,0</t>
+          <t>-54,22; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
